--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="215">
   <si>
     <t>Name</t>
   </si>
@@ -165,9 +165,6 @@
     <t>Slimey</t>
   </si>
   <si>
-    <t>Putrid</t>
-  </si>
-  <si>
     <t>Weakening</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
     <t>This unit is destroyed after 2 turns</t>
   </si>
   <si>
-    <t>Explosive</t>
-  </si>
-  <si>
     <t>Not enough tests</t>
   </si>
   <si>
@@ -384,9 +378,6 @@
     <t>All units damaged by attacks are pulled towards the unit</t>
   </si>
   <si>
-    <t>After dying, deals 1 (Fire) damage to ALL units within 1 cell</t>
-  </si>
-  <si>
     <t>Beckoned (X)</t>
   </si>
   <si>
@@ -429,9 +420,6 @@
     <t>Can deploy other units on this unit's position, but doing so takes 1 extra turn and destroys this unit</t>
   </si>
   <si>
-    <t>After dying, deals 1 (Poison) damage to ALL units within 1 cell</t>
-  </si>
-  <si>
     <t>The unit uses stats of "Polymorphed animal" but remains the same size. Expires at the end of opponent's turn or when polymorphed unit reaches 0 health</t>
   </si>
   <si>
@@ -643,6 +631,36 @@
   </si>
   <si>
     <t>Can be deployed in a line right behind or on the sides of enemy deployment zone, takes 1 extra turn to arrive this way</t>
+  </si>
+  <si>
+    <t>Crowd-dependant</t>
+  </si>
+  <si>
+    <t>""who needs attention</t>
+  </si>
+  <si>
+    <t>This unit's attack damage is always equal to the number of nearby cells occupied by friendly units</t>
+  </si>
+  <si>
+    <t>Ratbearer</t>
+  </si>
+  <si>
+    <t>ratbearer ""</t>
+  </si>
+  <si>
+    <t>Creates a "Virus rat" unit nearby for every destroyed unit within 1 cell</t>
+  </si>
+  <si>
+    <t>Explosive (X)</t>
+  </si>
+  <si>
+    <t>After dying, deals X (Fire) damage to ALL units within 1 cell</t>
+  </si>
+  <si>
+    <t>Putrid (X)</t>
+  </si>
+  <si>
+    <t>After dying, deals X (Poison) damage to ALL units within 1 cell</t>
   </si>
 </sst>
 </file>
@@ -1176,23 +1194,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J137"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J142"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="3"/>
-    <col min="3" max="3" width="16.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="72.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="16.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="72.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.85546875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="3"/>
+    <col min="8" max="8" width="12.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44.88671875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -1206,7 +1224,7 @@
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1214,7 +1232,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1234,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1283,7 +1301,7 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -1304,12 +1322,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,32 +1347,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1377,7 +1395,7 @@
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -1389,7 +1407,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1398,14 +1416,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
@@ -1423,35 +1441,35 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -1472,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1483,16 +1501,16 @@
         <v>6</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
@@ -1532,24 +1550,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1563,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1572,7 +1590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
@@ -1592,27 +1610,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1632,7 +1650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="43.15" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1643,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>6</v>
@@ -1652,7 +1670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C29" s="8" t="s">
         <v>0</v>
       </c>
@@ -1672,27 +1690,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C30" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C31" s="8" t="s">
         <v>5</v>
       </c>
@@ -1717,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
@@ -1729,10 +1747,10 @@
         <v>6</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C34" s="8" t="s">
         <v>0</v>
       </c>
@@ -1749,30 +1767,30 @@
         <v>0</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C36" s="8" t="s">
         <v>5</v>
       </c>
@@ -1792,7 +1810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
       <c r="C37" s="8" t="s">
         <v>6</v>
       </c>
@@ -1812,7 +1830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C39" s="8" t="s">
         <v>0</v>
       </c>
@@ -1823,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>60</v>
+        <v>211</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
@@ -1832,24 +1850,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="3:10" s="13" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C40" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1872,27 +1890,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="7" t="s">
-        <v>122</v>
+      <c r="G42" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
@@ -1903,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>0</v>
@@ -1912,27 +1930,27 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C45" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1952,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C47" s="4" t="s">
         <v>6</v>
       </c>
@@ -1963,16 +1981,16 @@
         <v>6</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" ht="15" x14ac:dyDescent="0.25">
       <c r="C49" s="8" t="s">
         <v>0</v>
       </c>
@@ -1983,36 +2001,36 @@
         <v>0</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="C50" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C51" s="8" t="s">
         <v>5</v>
       </c>
@@ -2032,35 +2050,35 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C52" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F53" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="F53" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C54" s="4" t="s">
         <v>0</v>
       </c>
@@ -2068,39 +2086,39 @@
         <v>45</v>
       </c>
       <c r="F54" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G55" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C55" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="I55" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2114,61 +2132,61 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C59" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C61" s="8" t="s">
         <v>5</v>
       </c>
@@ -2193,62 +2211,62 @@
         <v>6</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C64" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C65" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="F65" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
         <v>5</v>
       </c>
@@ -2268,67 +2286,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C67" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C70" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C71" s="4" t="s">
         <v>5</v>
       </c>
@@ -2348,67 +2366,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="75" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C75" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2428,67 +2446,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="79" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="C79" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="I79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="80" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C80" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2508,67 +2526,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C84" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C84" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="s">
+      <c r="I84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="I85" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C86" s="7" t="s">
         <v>5</v>
       </c>
@@ -2588,59 +2606,59 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C87" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F88" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="C89" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F89" s="18"/>
       <c r="G89" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F90" s="18"/>
       <c r="G90" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.3">
       <c r="C91" s="7" t="s">
         <v>5</v>
       </c>
@@ -2649,64 +2667,64 @@
       </c>
       <c r="F91" s="19"/>
       <c r="G91" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C92" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F93" s="11"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="95" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C95" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="96" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2726,73 +2744,73 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="43.15" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="98" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C98"/>
       <c r="D98"/>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="100" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C100" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2812,67 +2830,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="3:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="104" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="105" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C105" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="106" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2892,43 +2910,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F109" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F110" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G110" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="109" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="F109" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="110" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="F110" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="111" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2936,31 +2954,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="43.15" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="F112" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="114" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="114" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F114" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="115" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="115" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F115" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="116" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="116" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2968,31 +2986,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F117" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G117" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="119" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F119" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G119" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="119" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="F119" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="120" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F120" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="121" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10" x14ac:dyDescent="0.3">
       <c r="F121" s="4" t="s">
         <v>5</v>
       </c>
@@ -3000,55 +3018,55 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F122" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G122" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C124" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="124" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C124" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>193</v>
-      </c>
       <c r="F124" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G124" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="I124" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C125" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="126" spans="3:10" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="126" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C126" s="4" t="s">
         <v>5</v>
       </c>
@@ -3068,83 +3086,101 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="128" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="128" spans="3:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C128" s="4"/>
       <c r="D128" s="15" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="129" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="129" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C129" s="4"/>
       <c r="D129" s="15" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="130" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="130" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C130"/>
       <c r="D130"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="134" spans="3:10" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C134" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="F134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J134" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="135" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C135" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G135" s="4" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="135" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F135" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="I135" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="136" spans="3:10" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="136" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C136" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F136" s="4" t="s">
         <v>5</v>
       </c>
@@ -3158,18 +3194,56 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="3:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="F137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G137" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="139" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F139" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="140" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F140" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="141" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="F141" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="3:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="I137" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -3185,9 +3259,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3197,7 +3271,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -258,15 +258,9 @@
     <t xml:space="preserve">Hydrokinesis </t>
   </si>
   <si>
-    <t>When moving, all "Water" covers within 3 cells move in the same relative direction</t>
-  </si>
-  <si>
     <t>Oliokinesis</t>
   </si>
   <si>
-    <t>When moving, all "Oil" covers within 3 cells move in the same relative direction</t>
-  </si>
-  <si>
     <t>After attacking a cell, covers it in "Storm cloud"</t>
   </si>
   <si>
@@ -661,6 +655,12 @@
   </si>
   <si>
     <t>After dying, deals X (Poison) damage to ALL units within 1 cell</t>
+  </si>
+  <si>
+    <t>When moving, all "Water" covers within 3 cells extend in the same movement direction</t>
+  </si>
+  <si>
+    <t>When moving, all "Oil" covers within 3 cells extend in the same movement direction</t>
   </si>
 </sst>
 </file>
@@ -1195,22 +1195,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J142"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="3"/>
-    <col min="3" max="3" width="16.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="72.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="3"/>
+    <col min="3" max="3" width="16.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="72.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="45" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="44.88671875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="3"/>
+    <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="44.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -1224,7 +1224,7 @@
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1232,7 +1232,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1252,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -1322,12 +1322,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1347,32 +1347,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
@@ -1407,7 +1407,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1416,14 +1416,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
@@ -1441,35 +1441,35 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -1490,7 +1490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1501,16 +1501,16 @@
         <v>6</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C20" s="2" t="s">
         <v>5</v>
       </c>
@@ -1550,24 +1550,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1590,7 +1590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
@@ -1610,27 +1610,27 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" ht="43.15" x14ac:dyDescent="0.3">
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C29" s="8" t="s">
         <v>0</v>
       </c>
@@ -1690,27 +1690,27 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C30" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C31" s="8" t="s">
         <v>5</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
@@ -1750,7 +1750,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C34" s="8" t="s">
         <v>0</v>
       </c>
@@ -1770,27 +1770,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C36" s="8" t="s">
         <v>5</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="3:10" ht="28.95" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:10" ht="28.9" x14ac:dyDescent="0.3">
       <c r="C37" s="8" t="s">
         <v>6</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C39" s="8" t="s">
         <v>0</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
@@ -1850,24 +1850,24 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="3:10" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:10" s="13" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C40" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1890,27 +1890,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>0</v>
@@ -1930,27 +1930,27 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C45" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C46" s="4" t="s">
         <v>5</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C47" s="4" t="s">
         <v>6</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>6</v>
@@ -1990,17 +1990,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="3:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C49" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="s">
+      <c r="F49" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="s">
         <v>67</v>
       </c>
       <c r="I49" s="7" t="s">
@@ -2010,37 +2010,37 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="3:10" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C50" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>90</v>
+        <v>101</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="3:10" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C51" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="7" t="s">
+      <c r="F51" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I51" s="7" t="s">
@@ -2050,45 +2050,45 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C52" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="8" t="s">
         <v>68</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="F53" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F53" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C54" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="8" t="s">
         <v>72</v>
       </c>
       <c r="I54" s="4" t="s">
@@ -2098,27 +2098,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F55" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="8" t="s">
         <v>74</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C56" s="4" t="s">
         <v>5</v>
       </c>
@@ -2132,21 +2132,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C59" s="8" t="s">
         <v>0</v>
       </c>
@@ -2166,27 +2166,27 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C61" s="8" t="s">
         <v>5</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="3:10" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:10" ht="60" x14ac:dyDescent="0.25">
       <c r="C62" s="8" t="s">
         <v>6</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>6</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>6</v>
@@ -2226,17 +2226,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C64" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="s">
+      <c r="F64" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8" t="s">
         <v>79</v>
       </c>
       <c r="I64" s="4" t="s">
@@ -2246,37 +2246,37 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C65" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>109</v>
+      <c r="F65" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C66" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" s="4" t="s">
+      <c r="F66" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I66" s="4" t="s">
@@ -2286,18 +2286,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="C67" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>80</v>
+        <v>130</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>213</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
@@ -2306,18 +2306,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C69" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>81</v>
+      <c r="F69" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>0</v>
@@ -2326,37 +2326,37 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>110</v>
+        <v>88</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C71" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="4" t="s">
+      <c r="F71" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I71" s="8" t="s">
@@ -2366,27 +2366,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="3:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:10" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>82</v>
+        <v>172</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>214</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C74" s="4" t="s">
         <v>0</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>0</v>
@@ -2406,27 +2406,27 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C76" s="4" t="s">
         <v>5</v>
       </c>
@@ -2446,18 +2446,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>6</v>
@@ -2466,7 +2466,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C79" s="4" t="s">
         <v>0</v>
       </c>
@@ -2477,36 +2477,36 @@
         <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C81" s="4" t="s">
         <v>5</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C82" s="4" t="s">
         <v>6</v>
       </c>
@@ -2537,56 +2537,56 @@
         <v>6</v>
       </c>
       <c r="G82" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C84" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I82" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="84" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C84" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G84" s="4" t="s">
+      <c r="I84" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C85" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I84" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C85" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="I85" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C86" s="7" t="s">
         <v>5</v>
       </c>
@@ -2606,59 +2606,59 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C87" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="88" spans="3:10" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F88" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F89" s="18"/>
       <c r="G89" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="90" spans="3:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F90" s="18"/>
       <c r="G90" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
       <c r="C91" s="7" t="s">
         <v>5</v>
       </c>
@@ -2667,64 +2667,64 @@
       </c>
       <c r="F91" s="19"/>
       <c r="G91" s="9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="92" spans="3:10" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C92" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
     </row>
-    <row r="93" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F93" s="11"/>
       <c r="G93"/>
     </row>
-    <row r="94" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="95" spans="3:10" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="96" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C96" s="4" t="s">
         <v>5</v>
       </c>
@@ -2744,73 +2744,73 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:10" ht="60" x14ac:dyDescent="0.25">
       <c r="C97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="98" spans="3:10" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C98"/>
       <c r="D98"/>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
     </row>
-    <row r="99" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="100" spans="3:10" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="101" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C101" s="4" t="s">
         <v>5</v>
       </c>
@@ -2830,67 +2830,67 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="3:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="104" spans="3:10" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="105" spans="3:10" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="106" spans="3:10" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C106" s="4" t="s">
         <v>5</v>
       </c>
@@ -2910,43 +2910,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="109" spans="3:10" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="109" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F109" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="110" spans="3:10" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F110" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="111" spans="3:10" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="111" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F111" s="4" t="s">
         <v>5</v>
       </c>
@@ -2954,31 +2954,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="3:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="F112" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="114" spans="3:10" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="114" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F114" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="115" spans="3:10" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="115" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F115" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="116" spans="3:10" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="116" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F116" s="4" t="s">
         <v>5</v>
       </c>
@@ -2986,31 +2986,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="F117" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="119" spans="3:10" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="119" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F119" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="120" spans="3:10" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="120" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F120" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="121" spans="3:10" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="121" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F121" s="4" t="s">
         <v>5</v>
       </c>
@@ -3018,55 +3018,55 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="F122" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="124" spans="3:10" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="124" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C124" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D124" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F124" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>191</v>
-      </c>
       <c r="I124" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="125" spans="3:10" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C125" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="126" spans="3:10" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="126" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C126" s="4" t="s">
         <v>5</v>
       </c>
@@ -3086,95 +3086,95 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="128" spans="3:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="128" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="4"/>
       <c r="D128" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="129" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="129" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C129" s="4"/>
       <c r="D129" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="130" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="130" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C130"/>
       <c r="D130"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="134" spans="3:10" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="134" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="135" spans="3:10" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="135" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C135" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="136" spans="3:10" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="136" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C136" s="4" t="s">
         <v>5</v>
       </c>
@@ -3194,43 +3194,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="3:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G137" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="F139" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G139" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="I137" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="139" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="F139" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="140" spans="3:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F140" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="141" spans="3:10" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="141" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F141" s="4" t="s">
         <v>5</v>
       </c>
@@ -3238,12 +3238,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="3:10" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:10" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F142" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3259,9 +3259,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3271,7 +3271,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="217">
   <si>
     <t>Name</t>
   </si>
@@ -661,6 +661,12 @@
   </si>
   <si>
     <t>When moving, all "Oil" covers within 3 cells extend in the same movement direction</t>
+  </si>
+  <si>
+    <t>Slow-handed</t>
+  </si>
+  <si>
+    <t>After attacking, this unit's attack damage is reduced to 0 and then gradually increases to the normal amount (1 dmg each round)</t>
   </si>
 </sst>
 </file>
@@ -1870,7 +1876,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="8" t="s">
         <v>5</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="8" t="s">
         <v>6</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
         <v>87</v>
       </c>
@@ -3221,6 +3227,12 @@
       <c r="G139" s="4" t="s">
         <v>203</v>
       </c>
+      <c r="I139" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="140" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F140" s="4" t="s">
@@ -3229,6 +3241,12 @@
       <c r="G140" s="4" t="s">
         <v>204</v>
       </c>
+      <c r="I140" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="J140" s="4" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="141" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F141" s="4" t="s">
@@ -3237,6 +3255,12 @@
       <c r="G141" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="I141" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="142" spans="3:10" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F142" s="4" t="s">
@@ -3244,6 +3268,12 @@
       </c>
       <c r="G142" s="4" t="s">
         <v>205</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J142" s="4" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -3221,10 +3221,10 @@
       </c>
     </row>
     <row r="139" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F139" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G139" s="4" t="s">
+      <c r="F139" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G139" s="7" t="s">
         <v>203</v>
       </c>
       <c r="I139" s="4" t="s">
@@ -3235,10 +3235,10 @@
       </c>
     </row>
     <row r="140" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F140" s="4" t="s">
+      <c r="F140" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="G140" s="7" t="s">
         <v>204</v>
       </c>
       <c r="I140" s="4" t="s">
@@ -3249,10 +3249,10 @@
       </c>
     </row>
     <row r="141" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F141" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G141" s="4" t="s">
+      <c r="F141" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G141" s="7" t="s">
         <v>8</v>
       </c>
       <c r="I141" s="4" t="s">
@@ -3263,10 +3263,10 @@
       </c>
     </row>
     <row r="142" spans="3:10" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F142" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G142" s="4" t="s">
+      <c r="F142" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="7" t="s">
         <v>205</v>
       </c>
       <c r="I142" s="4" t="s">

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="220">
   <si>
     <t>Name</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Protected</t>
   </si>
   <si>
-    <t>Oozing</t>
-  </si>
-  <si>
     <t>Dripping</t>
   </si>
   <si>
@@ -153,18 +150,12 @@
     <t>Can move through other units</t>
   </si>
   <si>
-    <t>Teleportation beacon</t>
-  </si>
-  <si>
     <t>Immovable</t>
   </si>
   <si>
     <t>Cannot be moved by any means</t>
   </si>
   <si>
-    <t>Slimey</t>
-  </si>
-  <si>
     <t>Weakening</t>
   </si>
   <si>
@@ -288,9 +279,6 @@
     <t>Slippery ""</t>
   </si>
   <si>
-    <t>"" oozing with oil</t>
-  </si>
-  <si>
     <t>Blind ""</t>
   </si>
   <si>
@@ -300,9 +288,6 @@
     <t>"" what is actually 3 goblins</t>
   </si>
   <si>
-    <t>"" slimey with toxin</t>
-  </si>
-  <si>
     <t>cowardly ""</t>
   </si>
   <si>
@@ -667,6 +652,30 @@
   </si>
   <si>
     <t>After attacking, this unit's attack damage is reduced to 0 and then gradually increases to the normal amount (1 dmg each round)</t>
+  </si>
+  <si>
+    <t>Cheap</t>
+  </si>
+  <si>
+    <t>cheap ""</t>
+  </si>
+  <si>
+    <t>Oily</t>
+  </si>
+  <si>
+    <t>oiled ""</t>
+  </si>
+  <si>
+    <t>toxic ""</t>
+  </si>
+  <si>
+    <t>Toxic</t>
+  </si>
+  <si>
+    <t>Beacon</t>
+  </si>
+  <si>
+    <t>After deploying this unit, you can select another unit with "Cheap" to be deployed</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -1258,28 +1267,28 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1307,13 +1316,13 @@
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -1325,7 +1334,7 @@
         <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1338,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>23</v>
+        <v>214</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>0</v>
@@ -1353,32 +1362,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1401,19 +1410,19 @@
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>6</v>
@@ -1424,12 +1433,12 @@
     </row>
     <row r="13" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>0</v>
@@ -1441,41 +1450,41 @@
         <v>0</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>5</v>
@@ -1507,16 +1516,16 @@
         <v>6</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1556,24 +1565,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C21" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="3:10" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1587,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>6</v>
@@ -1601,39 +1610,39 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1661,19 +1670,19 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1687,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>0</v>
@@ -1698,22 +1707,22 @@
     </row>
     <row r="30" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C30" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1741,19 +1750,19 @@
         <v>6</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1761,39 +1770,39 @@
         <v>0</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C35" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1821,19 +1830,19 @@
         <v>6</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
@@ -1841,39 +1850,39 @@
         <v>0</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="3:10" s="13" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
       <c r="C40" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1901,19 +1910,19 @@
         <v>6</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="3:10" x14ac:dyDescent="0.25">
@@ -1921,39 +1930,39 @@
         <v>0</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>211</v>
+        <v>39</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>99</v>
+        <v>85</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="3:10" x14ac:dyDescent="0.25">
@@ -1963,10 +1972,10 @@
       <c r="D46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G46" s="4" t="s">
+      <c r="F46" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I46" s="8" t="s">
@@ -1981,19 +1990,19 @@
         <v>6</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>212</v>
+        <v>40</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="3:10" x14ac:dyDescent="0.25">
@@ -2001,39 +2010,39 @@
         <v>0</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>0</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C50" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="3:10" x14ac:dyDescent="0.25">
@@ -2061,27 +2070,27 @@
         <v>6</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>6</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F53" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="3:10" x14ac:dyDescent="0.25">
@@ -2089,39 +2098,39 @@
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C55" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="3:10" x14ac:dyDescent="0.25">
@@ -2143,13 +2152,13 @@
         <v>6</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="3:10" x14ac:dyDescent="0.25">
@@ -2157,39 +2166,39 @@
         <v>0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="3:10" s="10" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="3:10" x14ac:dyDescent="0.25">
@@ -2217,19 +2226,19 @@
         <v>6</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="3:10" x14ac:dyDescent="0.25">
@@ -2237,39 +2246,39 @@
         <v>0</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C65" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="3:10" x14ac:dyDescent="0.25">
@@ -2297,19 +2306,19 @@
         <v>6</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="3:10" x14ac:dyDescent="0.25">
@@ -2317,39 +2326,39 @@
         <v>0</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>0</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I69" s="8" t="s">
         <v>0</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C70" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="3:10" x14ac:dyDescent="0.25">
@@ -2377,19 +2386,19 @@
         <v>6</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>6</v>
       </c>
       <c r="J72" s="8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="3:10" x14ac:dyDescent="0.25">
@@ -2397,39 +2406,39 @@
         <v>0</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C75" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="F75" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="3:10" x14ac:dyDescent="0.25">
@@ -2457,19 +2466,19 @@
         <v>6</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="3:10" x14ac:dyDescent="0.25">
@@ -2477,39 +2486,39 @@
         <v>0</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="80" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C80" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="3:10" x14ac:dyDescent="0.25">
@@ -2537,19 +2546,19 @@
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="3:10" x14ac:dyDescent="0.25">
@@ -2557,39 +2566,39 @@
         <v>0</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C85" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="3:10" x14ac:dyDescent="0.25">
@@ -2617,27 +2626,27 @@
         <v>6</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="3:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F88" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="3:10" ht="24" x14ac:dyDescent="0.25">
@@ -2645,23 +2654,23 @@
         <v>0</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F89" s="18"/>
       <c r="G89" s="9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F90" s="18"/>
       <c r="G90" s="9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="3:10" ht="24" x14ac:dyDescent="0.25">
@@ -2673,7 +2682,7 @@
       </c>
       <c r="F91" s="19"/>
       <c r="G91" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="92" spans="3:10" x14ac:dyDescent="0.25">
@@ -2681,7 +2690,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F92" s="11"/>
       <c r="G92"/>
@@ -2695,39 +2704,39 @@
         <v>0</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="95" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C95" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="3:10" x14ac:dyDescent="0.25">
@@ -2755,19 +2764,19 @@
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="3:10" x14ac:dyDescent="0.25">
@@ -2781,39 +2790,39 @@
         <v>0</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C100" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="3:10" x14ac:dyDescent="0.25">
@@ -2841,19 +2850,19 @@
         <v>6</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="3:10" x14ac:dyDescent="0.25">
@@ -2861,39 +2870,39 @@
         <v>0</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="105" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C105" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="3:10" x14ac:dyDescent="0.25">
@@ -2921,19 +2930,19 @@
         <v>6</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="109" spans="3:10" x14ac:dyDescent="0.25">
@@ -2941,15 +2950,15 @@
         <v>0</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="110" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F110" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="3:10" x14ac:dyDescent="0.25">
@@ -2965,7 +2974,7 @@
         <v>6</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="114" spans="3:10" x14ac:dyDescent="0.25">
@@ -2973,15 +2982,15 @@
         <v>0</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F115" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="116" spans="3:10" x14ac:dyDescent="0.25">
@@ -2997,7 +3006,7 @@
         <v>6</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="3:10" x14ac:dyDescent="0.25">
@@ -3005,15 +3014,15 @@
         <v>0</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="120" spans="3:10" x14ac:dyDescent="0.25">
       <c r="F120" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="3:10" x14ac:dyDescent="0.25">
@@ -3029,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="124" spans="3:10" x14ac:dyDescent="0.25">
@@ -3037,39 +3046,39 @@
         <v>0</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="125" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C125" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="3:10" x14ac:dyDescent="0.25">
@@ -3097,39 +3106,39 @@
         <v>6</v>
       </c>
       <c r="D127" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J127" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="F127" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I127" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J127" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="128" spans="3:10" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="4"/>
       <c r="D128" s="15" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="129" spans="3:10" ht="30" x14ac:dyDescent="0.25">
       <c r="C129" s="4"/>
       <c r="D129" s="15" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="130" spans="3:10" ht="30" x14ac:dyDescent="0.25">
@@ -3137,7 +3146,7 @@
       <c r="D130"/>
       <c r="F130" s="4"/>
       <c r="G130" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="3:10" x14ac:dyDescent="0.25">
@@ -3145,39 +3154,39 @@
         <v>0</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="135" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C135" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="136" spans="3:10" x14ac:dyDescent="0.25">
@@ -3205,50 +3214,68 @@
         <v>6</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J137" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C139" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G139" s="7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="139" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="F139" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>203</v>
-      </c>
       <c r="I139" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="140" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C140" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="F140" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="141" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C141" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="F141" s="7" t="s">
         <v>5</v>
       </c>
@@ -3263,17 +3290,23 @@
       </c>
     </row>
     <row r="142" spans="3:10" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C142" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>219</v>
+      </c>
       <c r="F142" s="7" t="s">
         <v>6</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="223">
   <si>
     <t>Name</t>
   </si>
@@ -618,9 +618,6 @@
     <t>""who needs attention</t>
   </si>
   <si>
-    <t>This unit's attack damage is always equal to the number of nearby cells occupied by friendly units</t>
-  </si>
-  <si>
     <t>Ratbearer</t>
   </si>
   <si>
@@ -676,6 +673,18 @@
   </si>
   <si>
     <t>After deploying this unit, you can select another unit with "Cheap" to be deployed</t>
+  </si>
+  <si>
+    <t>Lethal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit's attack damage is equal to the total amount of attack damage between all friendly units within 1 cell </t>
+  </si>
+  <si>
+    <t>lethal ""</t>
+  </si>
+  <si>
+    <t>All succesfull attack damage dealt instantly destroys the target</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
@@ -1353,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>0</v>
@@ -1376,7 +1385,7 @@
         <v>84</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>84</v>
@@ -1536,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>0</v>
@@ -1576,7 +1585,7 @@
         <v>84</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>84</v>
@@ -1856,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>0</v>
@@ -1916,7 +1925,7 @@
         <v>6</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>6</v>
@@ -1936,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>0</v>
@@ -1996,7 +2005,7 @@
         <v>6</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>6</v>
@@ -2098,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>68</v>
@@ -2312,7 +2321,7 @@
         <v>6</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>6</v>
@@ -2392,7 +2401,7 @@
         <v>6</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I72" s="8" t="s">
         <v>6</v>
@@ -3154,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>0</v>
@@ -3174,7 +3183,7 @@
         <v>99</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>99</v>
@@ -3214,7 +3223,7 @@
         <v>6</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>6</v>
@@ -3230,11 +3239,11 @@
       </c>
     </row>
     <row r="139" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C139" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>212</v>
+      <c r="C139" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>0</v>
@@ -3246,15 +3255,15 @@
         <v>0</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C140" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>213</v>
+      <c r="C140" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>99</v>
@@ -3270,10 +3279,10 @@
       </c>
     </row>
     <row r="141" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C141" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="7" t="s">
+      <c r="C141" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D141" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F141" s="7" t="s">
@@ -3290,23 +3299,55 @@
       </c>
     </row>
     <row r="142" spans="3:10" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C142" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D142" s="7" t="s">
+      <c r="C142" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J142" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="144" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C144" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D144" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="F142" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G142" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I142" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J142" s="4" t="s">
-        <v>211</v>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C145" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C146" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C147" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/Abilities.xlsx
+++ b/Docs/Abilities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="226">
   <si>
     <t>Name</t>
   </si>
@@ -685,6 +685,15 @@
   </si>
   <si>
     <t>All succesfull attack damage dealt instantly destroys the target</t>
+  </si>
+  <si>
+    <t>Masochistic</t>
+  </si>
+  <si>
+    <t>masochistic ""</t>
+  </si>
+  <si>
+    <t>While this unit is below maximum health, add 1 damage to it's attack damage</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="3" customWidth="1"/>
@@ -1614,17 +1623,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="s">
+      <c r="F24" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I24" s="8" t="s">
@@ -1634,17 +1643,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="3:10" s="10" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="F25" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>34</v>
       </c>
       <c r="I25" s="8" t="s">
@@ -1654,17 +1663,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="3:10" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="7" t="s">
+      <c r="F26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I26" s="8" t="s">
@@ -1674,17 +1683,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="43.15" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:10" ht="45" x14ac:dyDescent="0.25">
       <c r="C27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="7" t="s">
+      <c r="F27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>63</v>
       </c>
       <c r="I27" s="8" t="s">
@@ -3348,6 +3357,38 @@
       </c>
       <c r="D147" s="7" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C149" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C150" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C151" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C152" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
